--- a/WIP Report/archive/WIP_Report_July_2026_H1.xlsx
+++ b/WIP Report/archive/WIP_Report_July_2026_H1.xlsx
@@ -759,7 +759,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:15:01</t>
+    <t>2026-07-16 10:03:19</t>
   </si>
   <si>
     <t>Source</t>

--- a/WIP Report/archive/WIP_Report_July_2026_H1.xlsx
+++ b/WIP Report/archive/WIP_Report_July_2026_H1.xlsx
@@ -759,7 +759,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:19</t>
+    <t>2026-07-16 15:22:53</t>
   </si>
   <si>
     <t>Source</t>
